--- a/requirements/M01.xlsx
+++ b/requirements/M01.xlsx
@@ -568,7 +568,7 @@
     <row r="2" ht="79.5" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="3" ht="79.5" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -838,7 +838,7 @@
     <row r="4" ht="79.5" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -960,7 +960,7 @@
     <row r="5" ht="79.5" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="6" ht="79.5" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="7" ht="79.5" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="8" ht="79.5" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="9" ht="79.5" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1632,7 +1632,7 @@
     <row r="10" ht="79.5" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1754,7 +1754,7 @@
     <row r="11" ht="79.5" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -1877,7 +1877,7 @@
     <row r="12" ht="79.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2008,7 +2008,7 @@
     <row r="13" ht="79.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -2135,7 +2135,7 @@
     <row r="14" ht="79.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2256,7 +2256,7 @@
     <row r="15" ht="79.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -2377,7 +2377,7 @@
     <row r="16" ht="79.5" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2500,7 +2500,7 @@
     <row r="17" ht="79.5" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
